--- a/NotasGeologiaPublicationList_Updated_1.xlsx
+++ b/NotasGeologiaPublicationList_Updated_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188A8259-F956-46CC-800C-BFA75CE96641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA472579-BCC4-4B6A-9F94-BD519D379F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5205" uniqueCount="4724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="4751">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14523,12 +14523,116 @@
       <t xml:space="preserve">ache localizado en el Río Orinoco, sectores Vuelta El Toro – El Merey, Municipio Sucre y Caicara del Orinoco – Puerto El Burro, Municipio Cedeño del Estado Bolívar. </t>
     </r>
   </si>
+  <si>
+    <t>Miocene turbidites in the Carapita Formation of eastern Venezuela.</t>
+  </si>
+  <si>
+    <t>James L. Lamb and John Sulek</t>
+  </si>
+  <si>
+    <t>Prepared for a presentation at the IV Caribbean Geological Conference, Trinidad, 1965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower Cretaceous microfauna from Trinidad and adjacent areas. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Howard Elwell Stacy </t>
+  </si>
+  <si>
+    <t>A dissertation submitted in partial fulfillment of the requirements for the degree of Doctor of Philosophy in the University of Michigan, 1966</t>
+  </si>
+  <si>
+    <t>Guías clases de Geología Física.</t>
+  </si>
+  <si>
+    <t>José Mas Vall</t>
+  </si>
+  <si>
+    <t>Guías preparadas para la asignatura Geología Física en la Escuela de Geología, Minas y Geofísica de la ilustre Universidad Central de Venezuela, 1975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis secuencial y correlación estratigráfica del Oligoceno Tardío del Norte de Monagas. </t>
+  </si>
+  <si>
+    <t>María Salomón Salazar y George P. Allen</t>
+  </si>
+  <si>
+    <t>Borrador de la presentación realizada a Lagoven S.A. en 1995</t>
+  </si>
+  <si>
+    <r>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en el subsuelo: Qué debemos saber de termodinámica, comportamiento de fase y principios de almacenamiento geológico. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Vega-Ortiz, C.; Rosales Rodríguez, J.; Larios Ferrer, J. L.; Navarro Tovar, L. G. </t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Suplemento Junio 2026</t>
+  </si>
+  <si>
+    <t>Distribution of major and trace elements in La Luna Formation, Southwestern Venezuela Basin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Mónaco, S.; López, L.; Rojas, H.; García, D.; Premovic, P.; Briceňo, H. </t>
+  </si>
+  <si>
+    <t>Organic Geochemistry, V. 33, pp. 1593 – 1608, 2002</t>
+  </si>
+  <si>
+    <t>En su 30 Aniversario El Parque Nacional El Avila aún refresca la capital.</t>
+  </si>
+  <si>
+    <t>Carta Ecológica Lagoven S. A., Número 46, Enero – Febrero, 1989</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#LambJLSulekJ1965</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#StacyHE1966</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#MasVallJ1975</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#SalomonMAllenGP1995</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/topics.html#VegaCetal2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geochemistry.html#LoMonacoSetal2002</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/ecology.html#Avila1989</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14587,6 +14691,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -14609,7 +14721,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -14622,6 +14734,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -46824,17 +46937,17 @@
       <c r="E1281" t="s">
         <v>4700</v>
       </c>
-      <c r="F1281" s="7" t="s">
+      <c r="F1281" s="8" t="s">
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1287" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1294" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1287" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1294" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -46849,7 +46962,7 @@
       <c r="E1282" t="s">
         <v>4703</v>
       </c>
-      <c r="F1282" s="7" t="s">
+      <c r="F1282" s="8" t="s">
         <v>4717</v>
       </c>
       <c r="G1282" s="1" t="str">
@@ -46874,7 +46987,7 @@
       <c r="E1283" t="s">
         <v>4706</v>
       </c>
-      <c r="F1283" s="7" t="s">
+      <c r="F1283" s="8" t="s">
         <v>4718</v>
       </c>
       <c r="G1283" s="1" t="str">
@@ -46896,7 +47009,7 @@
       <c r="E1284" t="s">
         <v>4708</v>
       </c>
-      <c r="F1284" s="7" t="s">
+      <c r="F1284" s="8" t="s">
         <v>4719</v>
       </c>
       <c r="G1284" s="1" t="str">
@@ -46921,7 +47034,7 @@
       <c r="E1285" t="s">
         <v>4710</v>
       </c>
-      <c r="F1285" s="7" t="s">
+      <c r="F1285" s="8" t="s">
         <v>4720</v>
       </c>
       <c r="G1285" s="1" t="str">
@@ -46946,7 +47059,7 @@
       <c r="E1286" t="s">
         <v>4713</v>
       </c>
-      <c r="F1286" s="7" t="s">
+      <c r="F1286" s="8" t="s">
         <v>4721</v>
       </c>
       <c r="G1286" s="1" t="str">
@@ -46968,7 +47081,7 @@
       <c r="E1287" t="s">
         <v>4715</v>
       </c>
-      <c r="F1287" s="7" t="s">
+      <c r="F1287" s="8" t="s">
         <v>4722</v>
       </c>
       <c r="G1287" s="1" t="str">
@@ -46977,41 +47090,175 @@
       </c>
     </row>
     <row r="1288" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1288" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1288" s="1"/>
+      <c r="A1288">
+        <f t="shared" si="42"/>
+        <v>1287</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>4724</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>4725</v>
+      </c>
+      <c r="D1288">
+        <v>1965</v>
+      </c>
+      <c r="E1288" t="s">
+        <v>4726</v>
+      </c>
+      <c r="F1288" s="8" t="s">
+        <v>4744</v>
+      </c>
+      <c r="G1288" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#LambJLSulekJ1965</v>
+      </c>
     </row>
     <row r="1289" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1289" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1289" s="1"/>
+      <c r="A1289">
+        <f t="shared" si="42"/>
+        <v>1288</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>4727</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>4728</v>
+      </c>
+      <c r="D1289">
+        <v>1966</v>
+      </c>
+      <c r="E1289" t="s">
+        <v>4729</v>
+      </c>
+      <c r="F1289" s="8" t="s">
+        <v>4745</v>
+      </c>
+      <c r="G1289" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#StacyHE1966</v>
+      </c>
     </row>
     <row r="1290" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1290" s="7" t="s">
-        <v>4315</v>
-      </c>
-      <c r="G1290" s="1"/>
+      <c r="A1290">
+        <f t="shared" si="42"/>
+        <v>1289</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>4730</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>4731</v>
+      </c>
+      <c r="D1290">
+        <v>1975</v>
+      </c>
+      <c r="E1290" t="s">
+        <v>4732</v>
+      </c>
+      <c r="F1290" s="8" t="s">
+        <v>4746</v>
+      </c>
+      <c r="G1290" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#MasVallJ1975</v>
+      </c>
     </row>
     <row r="1291" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1291" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1292" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1292" s="7" t="s">
-        <v>4315</v>
+      <c r="A1291">
+        <f t="shared" si="42"/>
+        <v>1290</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>4733</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>4734</v>
+      </c>
+      <c r="D1291">
+        <v>1995</v>
+      </c>
+      <c r="E1291" t="s">
+        <v>4735</v>
+      </c>
+      <c r="F1291" s="8" t="s">
+        <v>4747</v>
+      </c>
+      <c r="G1291" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#SalomonMAllenGP1995</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:7" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1292">
+        <f t="shared" si="42"/>
+        <v>1291</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>4736</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>4737</v>
+      </c>
+      <c r="D1292">
+        <v>2026</v>
+      </c>
+      <c r="E1292" t="s">
+        <v>4738</v>
+      </c>
+      <c r="F1292" s="8" t="s">
+        <v>4748</v>
+      </c>
+      <c r="G1292" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/topics.html#VegaCetal2026</v>
       </c>
     </row>
     <row r="1293" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1293" s="7" t="s">
-        <v>4315</v>
+      <c r="A1293">
+        <f t="shared" si="42"/>
+        <v>1292</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>4739</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>4740</v>
+      </c>
+      <c r="D1293">
+        <v>2002</v>
+      </c>
+      <c r="E1293" t="s">
+        <v>4741</v>
+      </c>
+      <c r="F1293" s="8" t="s">
+        <v>4749</v>
+      </c>
+      <c r="G1293" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geochemistry.html#LoMonacoSetal2002</v>
       </c>
     </row>
     <row r="1294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1294" s="7" t="s">
-        <v>4315</v>
+      <c r="A1294">
+        <f t="shared" si="42"/>
+        <v>1293</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>4742</v>
+      </c>
+      <c r="D1294">
+        <v>1989</v>
+      </c>
+      <c r="E1294" t="s">
+        <v>4743</v>
+      </c>
+      <c r="F1294" s="8" t="s">
+        <v>4750</v>
+      </c>
+      <c r="G1294" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/ecology.html#Avila1989</v>
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.3">
@@ -47447,16 +47694,7 @@
   </sheetData>
   <autoFilter ref="A1:G1267" xr:uid="{6B496A77-4B74-49B4-B08F-A7274E320005}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="F1281" r:id="rId1" location="Ayalaetal2010" xr:uid="{961B0CD1-124D-4C97-94CB-D327D72148B1}"/>
-    <hyperlink ref="F1282" r:id="rId2" location="LopezVMetal2003" xr:uid="{2F92AD89-067E-45B9-875B-AF47DEAD04ED}"/>
-    <hyperlink ref="F1283" r:id="rId3" location="StainforthRM1966" xr:uid="{F5664ED0-3F59-4F67-8AF3-C3A0E65CAA9C}"/>
-    <hyperlink ref="F1284" r:id="rId4" location="PromocionCajigal1945" xr:uid="{5984370C-BB6E-4CA0-8630-9AECDDFDAF0D}"/>
-    <hyperlink ref="F1285" r:id="rId5" location="MacsotayO1968a" xr:uid="{3CDD1149-4EBE-48E6-A408-B04868E6C0FC}"/>
-    <hyperlink ref="F1286" r:id="rId6" location="CastroMOdehnalM1987" xr:uid="{C9F42AF9-A565-4865-8D6D-48B025112588}"/>
-    <hyperlink ref="F1287" r:id="rId7" location="Costas1987" xr:uid="{8C448E11-3A46-4D58-9B4D-2BD8B435036C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/NotasGeologiaPublicationList_Updated_1.xlsx
+++ b/NotasGeologiaPublicationList_Updated_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA472579-BCC4-4B6A-9F94-BD519D379F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B836598C-D3CE-4F4E-B45A-49A75716B9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="4751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5240" uniqueCount="4770">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14626,6 +14626,63 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/ecology.html#Avila1989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principios y aplicaciones de los Métodos de Exploración Gravimétrico y Magnético. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Víctor Graterol </t>
+  </si>
+  <si>
+    <t>Libro de la Academia Nacional de la Ingeniería y el Hábitat de Venezuela, Caracas 2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geology of the Roraima Group and its implications. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santosh K. Ghosh </t>
+  </si>
+  <si>
+    <t>Volumen del Primer Simposio Amazónico, Puerto Ayacucho. Publicación Especial Número 10. Dirección General Sectorial de Geología y Minas, 1985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curso Básico Dinoflagelados. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. W. Van Erve y Armando Fasola </t>
+  </si>
+  <si>
+    <t>Intevep S.A., Julio 6 al 8 de 1988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolución diagenética de los carbonatos del Grupo Cogollo, Cuenca del Lago de Maracaibo. </t>
+  </si>
+  <si>
+    <t>Emma Kummerow y Daisy Pérez de Mejía 1987</t>
+  </si>
+  <si>
+    <t>Presentación realizada a Lagoven S.A., 1987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yacimientos petrolíferos de basamento. ¿Hasta dónde perforar? </t>
+  </si>
+  <si>
+    <t>: MAYA. Revista de Geociencias, Junio 2026</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/geophysics.html#GraterolV2022</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#GhoshSK1985</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#vanErveAWFasolaA1988</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/stratigraphy.html#KummerowEMejiaD1987</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/fields.html#PorrasJS2026</t>
   </si>
 </sst>
 </file>
@@ -46937,17 +46994,17 @@
       <c r="E1281" t="s">
         <v>4700</v>
       </c>
-      <c r="F1281" s="8" t="s">
+      <c r="F1281" t="s">
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1294" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1299" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
     <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1282">
-        <f t="shared" ref="A1282:A1294" si="42">A1281+1</f>
+        <f t="shared" ref="A1282:A1301" si="42">A1281+1</f>
         <v>1281</v>
       </c>
       <c r="B1282" t="s">
@@ -46962,7 +47019,7 @@
       <c r="E1282" t="s">
         <v>4703</v>
       </c>
-      <c r="F1282" s="8" t="s">
+      <c r="F1282" t="s">
         <v>4717</v>
       </c>
       <c r="G1282" s="1" t="str">
@@ -46987,7 +47044,7 @@
       <c r="E1283" t="s">
         <v>4706</v>
       </c>
-      <c r="F1283" s="8" t="s">
+      <c r="F1283" t="s">
         <v>4718</v>
       </c>
       <c r="G1283" s="1" t="str">
@@ -47009,7 +47066,7 @@
       <c r="E1284" t="s">
         <v>4708</v>
       </c>
-      <c r="F1284" s="8" t="s">
+      <c r="F1284" t="s">
         <v>4719</v>
       </c>
       <c r="G1284" s="1" t="str">
@@ -47034,7 +47091,7 @@
       <c r="E1285" t="s">
         <v>4710</v>
       </c>
-      <c r="F1285" s="8" t="s">
+      <c r="F1285" t="s">
         <v>4720</v>
       </c>
       <c r="G1285" s="1" t="str">
@@ -47059,7 +47116,7 @@
       <c r="E1286" t="s">
         <v>4713</v>
       </c>
-      <c r="F1286" s="8" t="s">
+      <c r="F1286" t="s">
         <v>4721</v>
       </c>
       <c r="G1286" s="1" t="str">
@@ -47081,7 +47138,7 @@
       <c r="E1287" t="s">
         <v>4715</v>
       </c>
-      <c r="F1287" s="8" t="s">
+      <c r="F1287" t="s">
         <v>4722</v>
       </c>
       <c r="G1287" s="1" t="str">
@@ -47106,7 +47163,7 @@
       <c r="E1288" t="s">
         <v>4726</v>
       </c>
-      <c r="F1288" s="8" t="s">
+      <c r="F1288" t="s">
         <v>4744</v>
       </c>
       <c r="G1288" s="1" t="str">
@@ -47131,7 +47188,7 @@
       <c r="E1289" t="s">
         <v>4729</v>
       </c>
-      <c r="F1289" s="8" t="s">
+      <c r="F1289" t="s">
         <v>4745</v>
       </c>
       <c r="G1289" s="1" t="str">
@@ -47156,7 +47213,7 @@
       <c r="E1290" t="s">
         <v>4732</v>
       </c>
-      <c r="F1290" s="8" t="s">
+      <c r="F1290" t="s">
         <v>4746</v>
       </c>
       <c r="G1290" s="1" t="str">
@@ -47181,7 +47238,7 @@
       <c r="E1291" t="s">
         <v>4735</v>
       </c>
-      <c r="F1291" s="8" t="s">
+      <c r="F1291" t="s">
         <v>4747</v>
       </c>
       <c r="G1291" s="1" t="str">
@@ -47206,7 +47263,7 @@
       <c r="E1292" t="s">
         <v>4738</v>
       </c>
-      <c r="F1292" s="8" t="s">
+      <c r="F1292" t="s">
         <v>4748</v>
       </c>
       <c r="G1292" s="1" t="str">
@@ -47231,7 +47288,7 @@
       <c r="E1293" t="s">
         <v>4741</v>
       </c>
-      <c r="F1293" s="8" t="s">
+      <c r="F1293" t="s">
         <v>4749</v>
       </c>
       <c r="G1293" s="1" t="str">
@@ -47253,7 +47310,7 @@
       <c r="E1294" t="s">
         <v>4743</v>
       </c>
-      <c r="F1294" s="8" t="s">
+      <c r="F1294" t="s">
         <v>4750</v>
       </c>
       <c r="G1294" s="1" t="str">
@@ -47262,91 +47319,191 @@
       </c>
     </row>
     <row r="1295" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1295" s="7" t="s">
-        <v>4315</v>
+      <c r="A1295">
+        <f t="shared" si="42"/>
+        <v>1294</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>4751</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>4752</v>
+      </c>
+      <c r="D1295">
+        <v>2022</v>
+      </c>
+      <c r="E1295" t="s">
+        <v>4753</v>
+      </c>
+      <c r="F1295" s="8" t="s">
+        <v>4765</v>
+      </c>
+      <c r="G1295" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/geophysics.html#GraterolV2022</v>
       </c>
     </row>
     <row r="1296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1296" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1297" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1297" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1298" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1298" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1299" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F1299" s="7" t="s">
-        <v>4315</v>
-      </c>
-    </row>
-    <row r="1300" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="A1296">
+        <f t="shared" si="42"/>
+        <v>1295</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>4754</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>4755</v>
+      </c>
+      <c r="D1296">
+        <v>1985</v>
+      </c>
+      <c r="E1296" t="s">
+        <v>4756</v>
+      </c>
+      <c r="F1296" s="8" t="s">
+        <v>4766</v>
+      </c>
+      <c r="G1296" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#GhoshSK1985</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1297">
+        <f t="shared" si="42"/>
+        <v>1296</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>4757</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>4758</v>
+      </c>
+      <c r="D1297">
+        <v>1988</v>
+      </c>
+      <c r="E1297" t="s">
+        <v>4759</v>
+      </c>
+      <c r="F1297" s="8" t="s">
+        <v>4767</v>
+      </c>
+      <c r="G1297" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#vanErveAWFasolaA1988</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1298">
+        <f t="shared" si="42"/>
+        <v>1297</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>4760</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>4761</v>
+      </c>
+      <c r="D1298">
+        <v>1987</v>
+      </c>
+      <c r="E1298" t="s">
+        <v>4762</v>
+      </c>
+      <c r="F1298" s="8" t="s">
+        <v>4768</v>
+      </c>
+      <c r="G1298" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/stratigraphy.html#KummerowEMejiaD1987</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1299">
+        <f t="shared" si="42"/>
+        <v>1298</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>4763</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D1299">
+        <v>2026</v>
+      </c>
+      <c r="E1299" t="s">
+        <v>4764</v>
+      </c>
+      <c r="F1299" s="8" t="s">
+        <v>4769</v>
+      </c>
+      <c r="G1299" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/fields.html#PorrasJS2026</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1300" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1301" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1301" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1302" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1302" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1303" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1303" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1304" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1304" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1305" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1305" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1306" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1306" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1307" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1307" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1308" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1308" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1309" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1309" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1310" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1310" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1311" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1311" s="7" t="s">
         <v>4315</v>
       </c>
     </row>
-    <row r="1312" spans="6:6" x14ac:dyDescent="0.3">
+    <row r="1312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F1312" s="7" t="s">
         <v>4315</v>
       </c>

--- a/NotasGeologiaPublicationList_Updated_1.xlsx
+++ b/NotasGeologiaPublicationList_Updated_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\Documents\GitHub\mariantoc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B836598C-D3CE-4F4E-B45A-49A75716B9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA996E2F-BE23-41CD-88A4-1C6D8A14F256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F60C23B-EB8B-4BF1-B197-717718F4FFB2}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5240" uniqueCount="4770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5245" uniqueCount="4777">
   <si>
     <t>Distribution of Mineral Occurrences in Northeastern South America</t>
   </si>
@@ -14667,9 +14667,6 @@
     <t xml:space="preserve">Yacimientos petrolíferos de basamento. ¿Hasta dónde perforar? </t>
   </si>
   <si>
-    <t>: MAYA. Revista de Geociencias, Junio 2026</t>
-  </si>
-  <si>
     <t>https://mariantoc.github.io/geophysics.html#GraterolV2022</t>
   </si>
   <si>
@@ -14683,6 +14680,30 @@
   </si>
   <si>
     <t>https://mariantoc.github.io/fields.html#PorrasJS2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Terremoto de Caracas de 1967: 50 año después. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Genatios; Marianela Lafuente; Alfredo Cilento; José Grases (compiladores) </t>
+  </si>
+  <si>
+    <t>Ediciones CITECI, Academia Nacional de la Ingeniería y el Hábitat, Caracas, junio 2017</t>
+  </si>
+  <si>
+    <t>MAYA. Revista de Geociencias, Junio 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En 1967 un violento terremoto afectó la capital venezolana y el litoral central. </t>
+  </si>
+  <si>
+    <t>Tomado de la página web de FUNVISIS. http://www.funvisis.gob.ve/old/reportaje7.php</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#GenatiosCetal2017</t>
+  </si>
+  <si>
+    <t>https://mariantoc.github.io/biography.html#FUNVISIS</t>
   </si>
 </sst>
 </file>
@@ -46998,7 +47019,7 @@
         <v>4716</v>
       </c>
       <c r="G1281" s="1" t="str">
-        <f t="shared" ref="G1281:G1299" si="41">HYPERLINK(F1281)</f>
+        <f t="shared" ref="G1281:G1301" si="41">HYPERLINK(F1281)</f>
         <v>https://mariantoc.github.io/minerals.html#Ayalaetal2010</v>
       </c>
     </row>
@@ -47335,8 +47356,8 @@
       <c r="E1295" t="s">
         <v>4753</v>
       </c>
-      <c r="F1295" s="8" t="s">
-        <v>4765</v>
+      <c r="F1295" t="s">
+        <v>4764</v>
       </c>
       <c r="G1295" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47360,8 +47381,8 @@
       <c r="E1296" t="s">
         <v>4756</v>
       </c>
-      <c r="F1296" s="8" t="s">
-        <v>4766</v>
+      <c r="F1296" t="s">
+        <v>4765</v>
       </c>
       <c r="G1296" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47385,8 +47406,8 @@
       <c r="E1297" t="s">
         <v>4759</v>
       </c>
-      <c r="F1297" s="8" t="s">
-        <v>4767</v>
+      <c r="F1297" t="s">
+        <v>4766</v>
       </c>
       <c r="G1297" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47410,8 +47431,8 @@
       <c r="E1298" t="s">
         <v>4762</v>
       </c>
-      <c r="F1298" s="8" t="s">
-        <v>4768</v>
+      <c r="F1298" t="s">
+        <v>4767</v>
       </c>
       <c r="G1298" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47433,10 +47454,10 @@
         <v>2026</v>
       </c>
       <c r="E1299" t="s">
-        <v>4764</v>
-      </c>
-      <c r="F1299" s="8" t="s">
-        <v>4769</v>
+        <v>4772</v>
+      </c>
+      <c r="F1299" t="s">
+        <v>4768</v>
       </c>
       <c r="G1299" s="1" t="str">
         <f t="shared" si="41"/>
@@ -47444,13 +47465,47 @@
       </c>
     </row>
     <row r="1300" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1300" s="7" t="s">
-        <v>4315</v>
+      <c r="A1300">
+        <f t="shared" si="42"/>
+        <v>1299</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>4769</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>4770</v>
+      </c>
+      <c r="D1300">
+        <v>2017</v>
+      </c>
+      <c r="E1300" t="s">
+        <v>4771</v>
+      </c>
+      <c r="F1300" s="8" t="s">
+        <v>4775</v>
+      </c>
+      <c r="G1300" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#GenatiosCetal2017</v>
       </c>
     </row>
     <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1301" s="7" t="s">
-        <v>4315</v>
+      <c r="A1301">
+        <f t="shared" si="42"/>
+        <v>1300</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>4773</v>
+      </c>
+      <c r="E1301" t="s">
+        <v>4774</v>
+      </c>
+      <c r="F1301" s="8" t="s">
+        <v>4776</v>
+      </c>
+      <c r="G1301" s="1" t="str">
+        <f t="shared" si="41"/>
+        <v>https://mariantoc.github.io/biography.html#FUNVISIS</v>
       </c>
     </row>
     <row r="1302" spans="1:7" x14ac:dyDescent="0.3">
